--- a/week-01/Ex4A_GTrends.xlsx
+++ b/week-01/Ex4A_GTrends.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0CFAE5EE-03DD-E742-A69B-843200BD8F58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{640AF213-EAF6-5743-84B8-4D3C901C2E9C}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="16660" xr2:uid="{640AF213-EAF6-5743-84B8-4D3C901C2E9C}"/>
   </bookViews>
   <sheets>
     <sheet name="GTrends_milkshake_hamburger_202" sheetId="1" r:id="rId1"/>
